--- a/private/planilla-comercio-2026.xlsx
+++ b/private/planilla-comercio-2026.xlsx
@@ -942,7 +942,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="8">
-        <f>=INDEX('Escala 2026'!$B$3:$J$23,MATCH(B5,'Escala 2026'!$A$3:$A$23,0),D6)*D5</f>
+        <f>INDEX('Escala 2026'!$B$3:$J$23,MATCH(B5,'Escala 2026'!$A$3:$A$23,0),D6)*D5</f>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -950,7 +950,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="8">
-        <f>=D7</f>
+        <f>D7</f>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -958,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="8">
-        <f>=(B12+B13)*B7*0.01</f>
+        <f>(B12+B13)*B7*0.01</f>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -966,7 +966,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="8">
-        <f>=IF(B9="Sí",(B12+B13+B14)/12,0)</f>
+        <f>IF(B9="Sí",(B12+B13+B14)/12,0)</f>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -974,7 +974,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="8">
-        <f>=D8</f>
+        <f>D8</f>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -982,7 +982,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="10">
-        <f>=B12+B13+B14+B15+B16</f>
+        <f>B12+B13+B14+B15+B16</f>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -990,7 +990,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="8">
-        <f>=-((B17-E7)*0.17+E7*0.03)</f>
+        <f>-((B17-E7)*0.17+E7*0.03)</f>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="10">
-        <f>=B17+B18</f>
+        <f>B17+B18</f>
       </c>
     </row>
     <row r="20" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1946,7 +1946,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="8">
-        <f>=B4/2*B5/B6</f>
+        <f>B4/2*B5/B6</f>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1954,7 +1954,7 @@
         <v>63</v>
       </c>
       <c r="B10" s="8">
-        <f>=-B9*0.17</f>
+        <f>-B9*0.17</f>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1962,7 +1962,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="10">
-        <f>=B9+B10</f>
+        <f>B9+B10</f>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">

--- a/private/planilla-comercio-2026.xlsx
+++ b/private/planilla-comercio-2026.xlsx
@@ -178,7 +178,7 @@
     <t>Vendedor D</t>
   </si>
   <si>
-    <t>Fuente: FAECYS — circular ACUERDO 07/2026 con las escalas de julio/2026 a mayo/2027 (28/7/2026) + Acuerdo paritario 22/7/2026 — CCT 130/75 (+5,7% trimestral + bono $50.000). Verificado el 30 de julio de 2026. La asignación extraordinaria es por única vez (julio y agosto de 2026) y no suma antigüedad, presentismo ni aguinaldo.</t>
+    <t>Fuente: FAECYS: circular ACUERDO 07/2026 con las escalas de julio/2026 a mayo/2027 (28/7/2026) + Acuerdo paritario 22/7/2026: CCT 130/75 (+5,7% trimestral + bono $50.000). Verificado el 30 de julio de 2026. La asignación extraordinaria es por única vez (julio y agosto de 2026) y no suma antigüedad, presentismo ni aguinaldo.</t>
   </si>
   <si>
     <t>Datos verificados contra los PDFs oficiales de FAECYS. calcular.ar · Operado por Hornero.</t>

--- a/private/planilla-comercio-2026.xlsx
+++ b/private/planilla-comercio-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="83">
   <si>
     <t>Liquidación de sueldos — Empleados de Comercio</t>
   </si>
@@ -31,63 +31,123 @@
     <t>Vendedor B</t>
   </si>
   <si>
+    <t>Maestranza A</t>
+  </si>
+  <si>
     <t>Mes a liquidar</t>
   </si>
   <si>
     <t>Diciembre 2026</t>
   </si>
   <si>
+    <t>Maestranza B</t>
+  </si>
+  <si>
     <t>Años de antigüedad</t>
   </si>
   <si>
+    <t>Maestranza C</t>
+  </si>
+  <si>
     <t>Jornada laboral</t>
   </si>
   <si>
     <t>Jornada completa (8hs)</t>
   </si>
   <si>
+    <t>Administrativo A</t>
+  </si>
+  <si>
     <t>¿Cobró presentismo?</t>
   </si>
   <si>
     <t>Sí</t>
   </si>
   <si>
+    <t>Administrativo B</t>
+  </si>
+  <si>
+    <t>Administrativo C</t>
+  </si>
+  <si>
     <t>LIQUIDACIÓN DEL MES</t>
   </si>
   <si>
+    <t>Administrativo D</t>
+  </si>
+  <si>
     <t>Básico convencional</t>
   </si>
   <si>
+    <t>Administrativo E</t>
+  </si>
+  <si>
     <t>Sumas no remunerativas</t>
   </si>
   <si>
+    <t>Administrativo F</t>
+  </si>
+  <si>
     <t>Adicional por antigüedad</t>
   </si>
   <si>
+    <t>Cajeros A</t>
+  </si>
+  <si>
     <t>Presentismo (8,33%)</t>
   </si>
   <si>
+    <t>Cajeros B</t>
+  </si>
+  <si>
     <t>Asignación extraordinaria</t>
   </si>
   <si>
+    <t>Cajeros C</t>
+  </si>
+  <si>
     <t>TOTAL BRUTO</t>
   </si>
   <si>
+    <t>Auxiliar A</t>
+  </si>
+  <si>
     <t>Aportes del trabajador</t>
   </si>
   <si>
+    <t>Auxiliar B</t>
+  </si>
+  <si>
     <t>NETO ESTIMADO</t>
   </si>
   <si>
+    <t>Auxiliar C</t>
+  </si>
+  <si>
+    <t>Auxiliar especializado A</t>
+  </si>
+  <si>
     <t>* Aportes = 17% jubilación+PAMI+obra social sobre lo remunerativo + 3% obra social sobre sumas no remunerativas (art. 40 CCT y acuerdo 26/3/2026).</t>
   </si>
   <si>
+    <t>Auxiliar especializado B</t>
+  </si>
+  <si>
     <t>* El neto es estimado: no incluye cuota sindical (FAECYS ~1%), Ganancias (si aplica) ni descuentos por deuda.</t>
   </si>
   <si>
+    <t>Vendedor A</t>
+  </si>
+  <si>
     <t>* Fuente: circular FAECYS 7/4/2026 + acuerdo paritario 26/3/2026. Verificado el 12/06/2026 contra los PDFs oficiales.</t>
   </si>
   <si>
+    <t>Vendedor C</t>
+  </si>
+  <si>
+    <t>Vendedor D</t>
+  </si>
+  <si>
     <t>Escala de básicos — CCT 130/75 Empleados de Comercio 2026</t>
   </si>
   <si>
@@ -116,66 +176,6 @@
   </si>
   <si>
     <t>Noviembre 2026</t>
-  </si>
-  <si>
-    <t>Maestranza A</t>
-  </si>
-  <si>
-    <t>Maestranza B</t>
-  </si>
-  <si>
-    <t>Maestranza C</t>
-  </si>
-  <si>
-    <t>Administrativo A</t>
-  </si>
-  <si>
-    <t>Administrativo B</t>
-  </si>
-  <si>
-    <t>Administrativo C</t>
-  </si>
-  <si>
-    <t>Administrativo D</t>
-  </si>
-  <si>
-    <t>Administrativo E</t>
-  </si>
-  <si>
-    <t>Administrativo F</t>
-  </si>
-  <si>
-    <t>Cajeros A</t>
-  </si>
-  <si>
-    <t>Cajeros B</t>
-  </si>
-  <si>
-    <t>Cajeros C</t>
-  </si>
-  <si>
-    <t>Auxiliar A</t>
-  </si>
-  <si>
-    <t>Auxiliar B</t>
-  </si>
-  <si>
-    <t>Auxiliar C</t>
-  </si>
-  <si>
-    <t>Auxiliar especializado A</t>
-  </si>
-  <si>
-    <t>Auxiliar especializado B</t>
-  </si>
-  <si>
-    <t>Vendedor A</t>
-  </si>
-  <si>
-    <t>Vendedor C</t>
-  </si>
-  <si>
-    <t>Vendedor D</t>
   </si>
   <si>
     <t>Fuente: FAECYS: circular ACUERDO 07/2026 con las escalas de julio/2026 a mayo/2027 (28/7/2026) + Acuerdo paritario 22/7/2026: CCT 130/75 (+5,7% trimestral + bono $50.000). Verificado el 30 de julio de 2026. La asignación extraordinaria es por única vez (julio y agosto de 2026) y no suma antigüedad, presentismo ni aguinaldo.</t>
@@ -842,13 +842,14 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="4" customWidth="1"/>
     <col min="4" max="5" width="20" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -869,7 +870,7 @@
       </c>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -882,13 +883,16 @@
       <c r="E5">
         <f>B13*B7*0.01</f>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <f>MATCH(B6,'Escala 2026'!$B$2:$J$2,0)</f>
@@ -896,10 +900,13 @@
       <c r="E6">
         <f>IF(B9="Sí",(B13+E5)/12,0)</f>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -910,115 +917,178 @@
       <c r="E7">
         <f>B13+E5+E6+B16</f>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <f>INDEX('Escala 2026'!$B$25:$J$25,1,D6)*D5</f>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <f>INDEX('Escala 2026'!$B$3:$J$23,MATCH(B5,'Escala 2026'!$A$3:$A$23,0),D6)*D5</f>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B13" s="8">
         <f>D7</f>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8">
         <f>(B12+B13)*B7*0.01</f>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B15" s="8">
         <f>IF(B9="Sí",(B12+B13+B14)/12,0)</f>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B16" s="8">
         <f>D8</f>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B17" s="10">
         <f>B12+B13+B14+B15+B16</f>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B18" s="8">
         <f>-((B17-E7)*0.17+E7*0.03)</f>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B19" s="10">
         <f>B17+B18</f>
       </c>
-    </row>
-    <row r="20" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" ht="6" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B21" s="11"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B22" s="11"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B23" s="11"/>
+      <c r="G23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1032,7 +1102,7 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" showErrorMessage="1" error="Seleccioná una categoría de la lista." sqref="B5">
-      <formula1>'Escala 2026'!$A$3:$A$23</formula1>
+      <formula1>'Liquidación'!$G$5:$G$25</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Seleccioná un mes de la lista." sqref="B6">
       <formula1>"Abril 2026,Mayo 2026,Junio 2026,Julio 2026,Agosto 2026,Septiembre 2026,Octubre 2026,Noviembre 2026,Diciembre 2026"</formula1>
@@ -1067,7 +1137,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -1081,39 +1151,39 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="B3" s="15">
         <v>1078911</v>
@@ -1145,7 +1215,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B4" s="17">
         <v>1082029</v>
@@ -1177,7 +1247,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B5" s="15">
         <v>1092951</v>
@@ -1209,7 +1279,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B6" s="17">
         <v>1090613</v>
@@ -1241,7 +1311,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="B7" s="15">
         <v>1095298</v>
@@ -1273,7 +1343,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B8" s="17">
         <v>1099977</v>
@@ -1305,7 +1375,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B9" s="15">
         <v>1114022</v>
@@ -1337,7 +1407,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B10" s="17">
         <v>1125724</v>
@@ -1369,7 +1439,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B11" s="15">
         <v>1142890</v>
@@ -1401,7 +1471,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B12" s="17">
         <v>1094513</v>
@@ -1433,7 +1503,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B13" s="15">
         <v>1099977</v>
@@ -1465,7 +1535,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B14" s="17">
         <v>1106999</v>
@@ -1497,7 +1567,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B15" s="15">
         <v>1094513</v>
@@ -1529,7 +1599,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B16" s="17">
         <v>1102315</v>
@@ -1561,7 +1631,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B17" s="15">
         <v>1128065</v>
@@ -1593,7 +1663,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B18" s="17">
         <v>1103879</v>
@@ -1625,7 +1695,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B19" s="15">
         <v>1117922</v>
@@ -1657,7 +1727,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B20" s="17">
         <v>1094513</v>
@@ -1721,7 +1791,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B22" s="17">
         <v>1125724</v>
@@ -1753,7 +1823,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B23" s="15">
         <v>1142890</v>
@@ -1785,7 +1855,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B24" s="19">
         <v>120000</v>
@@ -1817,7 +1887,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B25" s="19">
         <v>0</v>
